--- a/rental-calculator-settings-reference.xlsx
+++ b/rental-calculator-settings-reference.xlsx
@@ -107,9 +107,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -484,14 +482,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -524,7 +522,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALAYSIA LABOUR LAW — verified current as of September 2026</t>
+          <t>MALAYSIA LABOUR LAW &amp; TAX -- verified current as of September 2026</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -546,7 +544,7 @@
       <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Shown in the operator wage tooltip only</t>
+          <t>Reference note only</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -558,160 +556,133 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>EPF (KWSP) — employee rate</t>
+          <t>SOCSO / EIS wage ceiling</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>RM6,000 / month</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Folded into ESTIMATED_STATUTORY_MULTIPLIER_CITIZEN</t>
+          <t>Exact tables live in Overhead &amp; Manpower Calculator</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Third Schedule rounds up to next ringgit for wages under RM20,000.</t>
+          <t>Effective since Oct 2024.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>EPF — employer rate, wage ≤ RM5,000</t>
+          <t>Foreign worker EPF (employer)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Folded into ESTIMATED_STATUTORY_MULTIPLIER_CITIZEN</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+          <t>Not modeled on this page -- see below</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>NEW as of Oct 2025. KIV: belongs in Overhead &amp; Manpower Calculator if/when needed, not duplicated here.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>EPF — employer rate, wage &gt; RM5,000</t>
+          <t>SST on equipment rental/leasing</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>6% (toggle off by default)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Folded into ESTIMATED_STATUTORY_MULTIPLIER_CITIZEN</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>EPF — foreign worker (employer)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Folded into ESTIMATED_STATUTORY_MULTIPLIER_FOREIGN</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>NEW as of Oct 2025 — mandatory, was previously voluntary. Your other calculators don't model this yet.</t>
+          <t>rc-sst-pct default, rental-calculator.html</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Effective 1 Jan 2026. MSME exemption threshold: RM1.5 million rental revenue / 12 months.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>SOCSO / EIS wage ceiling</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>RM6,000 / month</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Exact banded tables live in Overhead &amp; Manpower Calculator, not here</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Effective since Oct 2024.</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>OPERATOR COST -- now a pure summary, not entered here</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Quick operator cost multiplier — citizen/PR</t>
+          <t>How operator cost is derived</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>×1.155</t>
+          <t>Shared manpower pool ÷ number of wet-hire machines</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>ESTIMATED_STATUTORY_MULTIPLIER_CITIZEN, rental-calculator.js</t>
+          <t>collectEquipment(), rental-calculator.js</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Fast estimate only (~15.5% combined EPF+SOCSO+EIS). For the exact figure, build one operator in Overhead &amp; Manpower Calculator and type their Employer Cost here instead.</t>
+          <t>2026-09-12: replaced the old per-machine wage + statutory-multiplier estimate entirely. Exact EPF/SOCSO/EIS math lives only in Overhead &amp; Manpower Calculator.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Quick operator cost multiplier — foreign worker</t>
+          <t>Foreign worker handling</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>×1.04</t>
+          <t>Not built on this page</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>ESTIMATED_STATUTORY_MULTIPLIER_FOREIGN, rental-calculator.js</t>
+          <t>KIV</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>EPF 2% employer + SOCSO, no EIS.</t>
+          <t>No wage field exists here any more to apply it to -- would belong in Overhead &amp; Manpower Calculator if needed later.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TAX</t>
+          <t>MARKET-RATE CONVERSION</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
@@ -722,246 +693,246 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>SST on equipment rental/leasing</t>
+          <t>Hours -&gt; daily conversion (hourly market rates)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>8 hours = 1 day</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>rc-sst-pct default value, rental-calculator.html</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Effective 1 Jan 2026 (was 8% for H2 2025). MSME exemption threshold: RM1.5 million rental revenue / 12 months. Toggle is OFF by default — turn on once you're registered/liable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>MARKET-RATE CONVERSION (for comparing rates quoted in different units)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+          <t>MARKET_RATE_HOURS_PER_DAY, rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Monthly -&gt; daily conversion (monthly market rates)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>÷ 26 days</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>MARKET_RATE_DAYS_PER_MONTH, rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Hours → daily conversion</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>8 hours = 1 day</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>MARKET_RATE_HOURS_PER_DAY, rental-calculator.js</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>A fixed reference for normalizing a competitor's hourly rate — independent of any one machine's own hours-per-day setting.</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PRICING TIERS -- new equipment starting values</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Monthly → daily conversion</t>
+          <t>Typical short-job length</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>÷ 26 days</t>
+          <t>3 days</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>MARKET_RATE_DAYS_PER_MONTH, rental-calculator.js</t>
+          <t>createEquipmentPanel(), .rc-eq-short-job-days</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Matches Malaysia's own standard working-day convention.</t>
+          <t>Spreads mobilization for the Daily tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Typical monthly-job length</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>26 days</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>createEquipmentPanel(), .rc-eq-monthly-job-days</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Spreads mobilization for the Monthly tier -- the main reason monthly is genuinely cheaper per day, not just discounted.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>REVENUE-SHARE PARTNERS — starting rows</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Hourly premium</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>createEquipmentPanel(), .rc-eq-hourly-premium-pct</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Applied on top of (daily price ÷ hours).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Partner 1</t>
+          <t>Extra monthly discount</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr">
         <is>
+          <t>createEquipmentPanel(), .rc-eq-monthly-discount-pct</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Applied on top of the mobilization-based saving, editable per machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>REVENUE-SHARE PARTNERS -- starting rows</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Partner 1 / 2 / 3</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>5% / 10% / 15%</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
           <t>seedDefaultPartners(), rental-calculator.js</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Pre-filled from the split found in your own reference spreadsheet. Rename/adjust freely — add or remove rows on the page itself.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Partner 2</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>seedDefaultPartners(), rental-calculator.js</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Partner 3</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>seedDefaultPartners(), rental-calculator.js</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>From your own reference spreadsheet. Rename/adjust freely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>MEMBER PRICING</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Member discount</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>rc-member-discount default, rental-calculator.html</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Pricing mode</t>
+          <t>Member discount</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Standard/member hits target margin; non-member pays more</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>rc-mode-protect, checked by default</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Matches how your own reference sheet already worked. Switch to “non-member hits target, member gets discount” on the page if you'd rather.</t>
-        </is>
-      </c>
+          <t>rc-member-discount default, rental-calculator.html</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Member deposit</t>
+          <t>Pricing mode</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>20% of standard price</t>
+          <t>Standard/member hits target margin; non-member pays more</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>rc-deposit-member-pct default</t>
+          <t>rc-mode-protect, checked by default</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Reference only — doesn't feed cost/margin math.</t>
+          <t>Matches your own reference sheet.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Non-member deposit</t>
+          <t>Member / non-member deposit</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>30% of non-member price</t>
+          <t>20% / 30%</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>rc-deposit-nonmember-pct default</t>
+          <t>rc-deposit-member-pct / rc-deposit-nonmember-pct defaults</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -969,7 +940,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>NEW EQUIPMENT — starting values (placeholders, not real data)</t>
+          <t>NEW EQUIPMENT -- starting values (placeholders, not real data)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
@@ -1113,12 +1084,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Wear &amp; tear reserve</t>
+          <t>Wear &amp; tear cost</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>RM8 / hour</t>
+          <t>RM20,000</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
@@ -1129,19 +1100,19 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>The one category your old Excel didn't have — undercarriage, hoses, bucket teeth, tires.</t>
+          <t>Restructured 2026-09-12 from a single RM/hour field -- entering a lump sum here used to become the per-hour rate by accident.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Unscheduled repair buffer</t>
+          <t>Wear &amp; tear covers</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>4,000 hours (= RM5/hour)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
@@ -1150,17 +1121,21 @@
           <t>createEquipmentPanel(), rental-calculator.js</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Restructured 2026-09-12 from a single RM/hour field -- entering a lump sum here used to become the per-hour rate by accident.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Operating hours / rental day</t>
+          <t>Unscheduled repair buffer</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
@@ -1174,12 +1149,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Operator basic wage</t>
+          <t>Operating hours / rental day</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RM2,200 / month</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
@@ -1250,12 +1225,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Spread mobilization over</t>
+          <t>Target margin</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>3 rental days</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr"/>
@@ -1266,173 +1241,130 @@
       </c>
       <c r="E45" s="4" t="inlineStr"/>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Target margin</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr"/>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>createEquipmentPanel(), rental-calculator.js</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr"/>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>COST-STRUCTURE GUIDE RATIOS (comparison only -- never feeds the price)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>COST-STRUCTURE GUIDE RATIOS (comparison only — never feeds the price)</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Mini excavator</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>55% equipment / 15% overhead / 12% operator / 18% margin</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>GUIDE_RATIOS.mini_excavator</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Mini excavator</t>
+          <t>Excavator</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>55% equipment / 15% overhead / 12% operator / 18% margin</t>
+          <t>50% equipment / 17% overhead / 13% operator / 20% margin</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>GUIDE_RATIOS.mini_excavator</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Rough rule of thumb, not a fact about your market — edit GUIDE_RATIOS directly if you have better numbers.</t>
-        </is>
-      </c>
+          <t>GUIDE_RATIOS.excavator</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Excavator</t>
+          <t>Backhoe loader</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>50% equipment / 17% overhead / 13% operator / 20% margin</t>
+          <t>48% equipment / 17% overhead / 15% operator / 20% margin</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>GUIDE_RATIOS.excavator</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Rough rule of thumb, not a fact about your market — edit GUIDE_RATIOS directly if you have better numbers.</t>
-        </is>
-      </c>
+          <t>GUIDE_RATIOS.backhoe_loader</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Backhoe loader</t>
+          <t>Crane</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>48% equipment / 17% overhead / 15% operator / 20% margin</t>
+          <t>45% equipment / 18% overhead / 17% operator / 20% margin</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr"/>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>GUIDE_RATIOS.backhoe_loader</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Rough rule of thumb, not a fact about your market — edit GUIDE_RATIOS directly if you have better numbers.</t>
-        </is>
-      </c>
+          <t>GUIDE_RATIOS.crane</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Crane</t>
+          <t>Forklift</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>45% equipment / 18% overhead / 17% operator / 20% margin</t>
+          <t>55% equipment / 15% overhead / 10% operator / 20% margin</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>GUIDE_RATIOS.crane</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Rough rule of thumb, not a fact about your market — edit GUIDE_RATIOS directly if you have better numbers.</t>
-        </is>
-      </c>
+          <t>GUIDE_RATIOS.forklift</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Forklift</t>
+          <t>Other / general</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>55% equipment / 15% overhead / 10% operator / 20% margin</t>
+          <t>50% equipment / 17% overhead / 13% operator / 20% margin</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>GUIDE_RATIOS.forklift</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Rough rule of thumb, not a fact about your market — edit GUIDE_RATIOS directly if you have better numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Other / general</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>50% equipment / 17% overhead / 13% operator / 20% margin</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
           <t>GUIDE_RATIOS.other</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>Rough rule of thumb, not a fact about your market — edit GUIDE_RATIOS directly if you have better numbers.</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1445,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1454,7 +1386,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>This workbook is a REFERENCE, not a live control panel — the site has no build step and no database, so nothing here is read automatically by the calculator (see AI_BUILD_BRIEF.md's own “nothing persists, no build step” rule).</t>
+          <t>This workbook is a REFERENCE, not a live control panel -- the site has no build step and no database, so nothing here is read automatically by the calculator.</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1396,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>What it's actually for: every default and constant in the Rental Calculator, in one place, so you (or anyone on your team) can see exactly what's being assumed without opening any code.</t>
+          <t>The “Your value” column is yours to fill in. Once decided, either type it directly into the live calculator (every one of these is an editable field on the page itself), or hand this to whoever maintains the code and point them at “Where it lives in the code.”</t>
         </is>
       </c>
     </row>
@@ -1474,31 +1406,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>The “Your value” column is yours to fill in with what YOU actually want a setting to be. Once you've decided, either:</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Type it directly into the live calculator (every one of these is an editable field on the page itself — no code needed for day-to-day use), or</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Hand this sheet to whoever maintains the code and ask them to update the constant listed in “Where it lives in the code.”</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Anything under NEW EQUIPMENT is just a starting point shown when you click “+ Add equipment” — it has nothing to do with your real machines. Type your real purchase price, residual value, etc. straight into the calculator; this sheet only controls what number shows up before you've touched it.</t>
+          <t>2026-09-12 update: operator cost is no longer entered per machine at all -- it's a summary pulled from the shared manpower pool (see the OPERATOR COST section). Wear &amp; tear is now a cost + interval pair, not a bare per-hour rate, specifically because a bare rate field is what caused an earlier absurd result.</t>
         </is>
       </c>
     </row>

--- a/rental-calculator-settings-reference.xlsx
+++ b/rental-calculator-settings-reference.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1365,6 +1365,226 @@
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>PARTNER PAYOUT TABLE -- 2026-09-13</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Which price basis is shown</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Wet only (dry splits the same %, just off a smaller base)</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>renderPartnerPayoutSection(), rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AD CREATOR -- 2026-09-13</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
+      <c r="C58" s="3" t="n"/>
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Canvas size</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>1080 x 1350px (4:5)</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>canvas width/height, rental-calculator.html</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Sized for Instagram/Facebook feed posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Header zone height</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>460px</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>HEADER_H, drawAdCanvas(), rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Footer zone height</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>150px</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>FOOTER_H, drawAdCanvas(), rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Default business name</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Reysourcez Enterprise</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>rc-ad-business default, rental-calculator.html</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Default tagline</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Heavy Machinery Rental</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>rc-ad-tagline default, rental-calculator.html</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Default contact</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>reysourcez.ent@gmail.com</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>rc-ad-contact default, rental-calculator.html</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Theme -- Site Teal</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Dark ink/teal + white</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>AD_THEMES.teal, rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Matches the rest of the site's own brand colors. Default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Theme -- Construction Amber</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Dark charcoal + amber</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>AD_THEMES.amber, rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Theme -- Steel Graphite</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Dark graphite + blue</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>AD_THEMES.graphite, rental-calculator.js</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
